--- a/result/XRCC3_LUSC_Tables.xlsx
+++ b/result/XRCC3_LUSC_Tables.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,17 +437,18 @@
           <t>Clinical Characteristics</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -462,6 +463,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -470,14 +472,17 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
         <v>109</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>79</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.006</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.008</t>
         </is>
       </c>
     </row>
@@ -488,12 +493,15 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
         <v>134</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>165</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -504,6 +512,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -512,14 +521,17 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.075</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.237</t>
         </is>
       </c>
     </row>
@@ -530,12 +542,15 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
         <v>53</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>73</v>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -544,12 +559,15 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
         <v>190</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>171</v>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -560,6 +578,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -568,14 +587,17 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
         <v>103</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>134</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.012</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.061</t>
         </is>
       </c>
     </row>
@@ -586,12 +608,15 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
         <v>82</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>74</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -600,12 +625,15 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
         <v>53</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>30</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -614,12 +642,15 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
         <v>3</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -630,6 +661,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -638,14 +670,17 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
         <v>201</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>199</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.995</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.919</t>
         </is>
       </c>
     </row>
@@ -656,12 +691,15 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -672,6 +710,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -680,14 +719,17 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
         <v>142</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>168</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.057</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.231</t>
         </is>
       </c>
     </row>
@@ -698,12 +740,15 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
         <v>70</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>56</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -712,12 +757,15 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
         <v>26</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>14</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -726,12 +774,15 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>3</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -742,6 +793,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -750,14 +802,17 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
         <v>42</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>66</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.047</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.077</t>
         </is>
       </c>
     </row>
@@ -768,12 +823,15 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
         <v>149</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>137</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -782,12 +840,15 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
         <v>41</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>29</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -796,12 +857,15 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
         <v>11</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>12</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -812,6 +876,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -820,14 +885,17 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
         <v>39</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>37</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.901</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.884</t>
         </is>
       </c>
     </row>
@@ -838,12 +906,15 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
         <v>205</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>207</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -882,32 +953,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>CDKN2AExpression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>SOX2Expression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PIK3CAExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>NOTCH1Expression</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>age</t>
         </is>
       </c>
     </row>
@@ -934,32 +1005,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>-0.118</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>-0.012</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.074</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.131</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>-0.017</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.047</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.118</t>
         </is>
       </c>
     </row>
@@ -978,32 +1049,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0.017</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.805</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.134</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.008</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.729</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.342</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.017</t>
         </is>
       </c>
     </row>
@@ -1030,32 +1101,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0.039</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-0.008</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>-0.040</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.020</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.004</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.039</t>
         </is>
       </c>
     </row>
@@ -1074,39 +1145,39 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>0.437</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>0.864</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.685</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.421</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.688</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.941</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.437</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1116,12 +1187,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.012</t>
+          <t>-0.118</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>0.039</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1131,27 +1202,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-0.145</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>-0.034</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.005</t>
         </is>
       </c>
     </row>
@@ -1164,45 +1235,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.437</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.967</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.495</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.915</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDKN2AExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1212,42 +1283,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>-0.039</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>-0.018</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.072</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>0.092</t>
         </is>
       </c>
     </row>
@@ -1260,45 +1331,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.805</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>0.063</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOX2Expression</t>
+          <t>CDKN2AExpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1308,42 +1379,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>-0.018</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>-0.006</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.555</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.145</t>
+          <t>-0.072</t>
         </is>
       </c>
     </row>
@@ -1356,45 +1427,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>0.685</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.967</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.901</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>0.601</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.145</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PIK3CAExpression</t>
+          <t>SOX2Expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1404,42 +1475,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-0.145</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>-0.006</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.555</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.035</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.034</t>
+          <t>0.013</t>
         </is>
       </c>
     </row>
@@ -1452,45 +1523,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.421</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.901</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>0.799</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOTCH1Expression</t>
+          <t>PIK3CAExpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1500,42 +1571,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>-0.034</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.072</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.555</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>-0.035</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.005</t>
         </is>
       </c>
     </row>
@@ -1548,45 +1619,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.495</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>0.601</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>0.476</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>NOTCH1Expression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1596,37 +1667,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.118</t>
+          <t>0.047</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.145</t>
+          <t>-0.072</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.034</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-0.035</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1644,37 +1715,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.342</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.941</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.915</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>0.799</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>0.476</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1690,7 +1761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,7 +1792,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.033</t>
         </is>
       </c>
     </row>
@@ -1732,86 +1803,176 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.797</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XRCC3group_Low</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.287</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.646</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>CDKN2AExpression</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.970</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pathologic_stage_2.0</t>
+          <t>SOX2Expression</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.037</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>0.165</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pathologic_stage_3.0</t>
+          <t>PIK3CAExpression</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.411</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.534</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>NOTCH1Expression</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.745</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>XRCC3group_High</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>505182.941</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.993</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>XRCC3group_Low</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>649083.7560000001</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.993</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.208</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pathologic_stage_2.0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.639</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.068</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>pathologic_stage_4.0</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2.942</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.022</t>
+      <c r="B14" t="n">
+        <v>2.992</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.020</t>
         </is>
       </c>
     </row>

--- a/result/XRCC3_LUSC_Tables.xlsx
+++ b/result/XRCC3_LUSC_Tables.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,404 +518,387 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">  FEMALE</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.104</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FEMALE</t>
+          <t xml:space="preserve">  MALE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="D7" t="n">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MALE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>190</v>
-      </c>
-      <c r="D8" t="n">
-        <v>171</v>
-      </c>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>103</v>
+      </c>
+      <c r="D9" t="n">
+        <v>134</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.061</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.061</t>
-        </is>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
+          <t>pathologic_M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pathologic_M</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>201</v>
+      </c>
+      <c r="D14" t="n">
+        <v>199</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.919</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>199</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.919</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
+          <t>pathologic_N</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pathologic_N</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>142</v>
+      </c>
+      <c r="D17" t="n">
+        <v>168</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.231</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="D18" t="n">
-        <v>168</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.231</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
+          <t>pathologic_T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pathologic_T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>42</v>
+      </c>
+      <c r="D22" t="n">
+        <v>66</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.077</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.077</t>
-        </is>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="D24" t="n">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>11</v>
-      </c>
-      <c r="D26" t="n">
-        <v>12</v>
-      </c>
+          <t>SmokingStatus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SmokingStatus</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>39</v>
+      </c>
+      <c r="D27" t="n">
+        <v>37</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.884</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="n">
-        <v>205</v>
-      </c>
-      <c r="D29" t="n">
         <v>207</v>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1000,37 +984,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.118</t>
+          <t>-0.109</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.012</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.102</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.037</t>
         </is>
       </c>
     </row>
@@ -1038,43 +1022,43 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>0.585</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.970</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.411</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1075,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1101,17 +1085,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1121,12 +1105,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
@@ -1134,43 +1118,43 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>0.585</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.802</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>0.981</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1171,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.118</t>
+          <t>-0.109</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1202,27 +1186,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.145</t>
+          <t>-0.116</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.034</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-0.012</t>
         </is>
       </c>
     </row>
@@ -1230,43 +1214,43 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>0.788</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>0.584</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>0.785</t>
         </is>
       </c>
     </row>
@@ -1283,17 +1267,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>-0.012</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-0.008</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1303,22 +1287,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.058</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.196</t>
         </is>
       </c>
     </row>
@@ -1326,43 +1310,43 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.970</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.802</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.200</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1363,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.102</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1404,17 +1388,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.072</t>
+          <t>-0.074</t>
         </is>
       </c>
     </row>
@@ -1422,43 +1406,43 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>0.788</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.104</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1459,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1485,17 +1469,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.145</t>
+          <t>-0.116</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.058</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1505,12 +1489,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>0.528</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.004</t>
         </is>
       </c>
     </row>
@@ -1518,32 +1502,32 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.200</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1554,7 +1538,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>0.933</t>
         </is>
       </c>
     </row>
@@ -1571,32 +1555,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.034</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>0.528</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1606,7 +1590,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.035</t>
+          <t>-0.032</t>
         </is>
       </c>
     </row>
@@ -1614,32 +1598,32 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>0.584</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1650,7 +1634,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>0.482</t>
         </is>
       </c>
     </row>
@@ -1667,37 +1651,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-0.074</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>0.004</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0.092</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-0.072</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.013</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.035</t>
+          <t>-0.032</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1710,42 +1694,42 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>0.981</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>0.785</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>0.933</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2918,4 +2902,99 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cancer Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chi-square</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>XRCC3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5.029</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.081</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>XRCC3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4.195</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.123</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/result/XRCC3_LUSC_Tables.xlsx
+++ b/result/XRCC3_LUSC_Tables.xlsx
@@ -2958,12 +2958,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.029</t>
+          <t>4.565</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.033</t>
         </is>
       </c>
     </row>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.195</t>
+          <t>1.724</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.189</t>
         </is>
       </c>
     </row>

--- a/result/XRCC3_LUSC_Tables.xlsx
+++ b/result/XRCC3_LUSC_Tables.xlsx
@@ -1745,7 +1745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1761,6 +1761,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>P-value</t>
         </is>
       </c>
@@ -1774,7 +1784,13 @@
       <c r="B2" t="n">
         <v>1.021</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>0.033</t>
         </is>
@@ -1789,7 +1805,13 @@
       <c r="B3" t="n">
         <v>1.001</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.797</t>
         </is>
@@ -1804,7 +1826,13 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.646</t>
         </is>
@@ -1819,7 +1847,13 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>0.970</t>
         </is>
@@ -1834,7 +1868,13 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.165</t>
         </is>
@@ -1849,7 +1889,13 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>0.534</t>
         </is>
@@ -1864,7 +1910,13 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.745</t>
         </is>
@@ -1879,7 +1931,15 @@
       <c r="B9" t="n">
         <v>505182.941</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>0.993</t>
         </is>
@@ -1894,7 +1954,15 @@
       <c r="B10" t="n">
         <v>649083.7560000001</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>0.993</t>
         </is>
@@ -1909,7 +1977,13 @@
       <c r="B11" t="n">
         <v>1.259</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.804</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>0.208</t>
         </is>
@@ -1924,7 +1998,13 @@
       <c r="B12" t="n">
         <v>1.088</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>0.639</t>
         </is>
@@ -1939,7 +2019,13 @@
       <c r="B13" t="n">
         <v>1.457</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.181</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>0.068</t>
         </is>
@@ -1954,7 +2040,13 @@
       <c r="B14" t="n">
         <v>2.992</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.541</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>0.020</t>
         </is>
@@ -2034,7 +2126,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XRCC3expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -2269,7 +2361,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XRCC3expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -2504,7 +2596,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XRCC3expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2739,7 +2831,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>XRCC3expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>

--- a/result/XRCC3_LUSC_Tables.xlsx
+++ b/result/XRCC3_LUSC_Tables.xlsx
@@ -10,8 +10,7 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2063,945 +2062,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Coefficient</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Lower</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>P-value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0349</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.5843e-02</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>847.3088</v>
-      </c>
-      <c r="C8" t="n">
-        <v>543.1007</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1151.5169</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>92.3857</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12.2633</v>
-      </c>
-      <c r="D9" t="n">
-        <v>172.508</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.024</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>37.7938</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-41.6969</v>
-      </c>
-      <c r="D10" t="n">
-        <v>117.2846</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.351</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>70.2186</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-29.0241</v>
-      </c>
-      <c r="D11" t="n">
-        <v>169.4614</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.165</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-84.5162</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-378.0097</v>
-      </c>
-      <c r="D12" t="n">
-        <v>208.9772</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.572</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-4.9509</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-9.2342</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.6676</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.024</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.4451</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.5705</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.6802</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.437</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0334</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3.1411e-02</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>857.9524</v>
-      </c>
-      <c r="C22" t="n">
-        <v>556.5856</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1159.3192</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>93.1567</v>
-      </c>
-      <c r="C23" t="n">
-        <v>12.5844</v>
-      </c>
-      <c r="D23" t="n">
-        <v>173.7291</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.024</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>10.7209</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-75.8443</v>
-      </c>
-      <c r="D24" t="n">
-        <v>97.2861</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.808</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>74.2885</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-47.1227</v>
-      </c>
-      <c r="D25" t="n">
-        <v>195.6997</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.230</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>-59.6083</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-246.2184</v>
-      </c>
-      <c r="D26" t="n">
-        <v>127.0018</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.530</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>-5.0534</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-9.2911</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-0.8157</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-0.3616</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.483</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.7599</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.527</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.0363</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2.1411e-02</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>837.4939000000001</v>
-      </c>
-      <c r="C36" t="n">
-        <v>530.8721</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1144.1157</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>92.765</v>
-      </c>
-      <c r="C37" t="n">
-        <v>12.8455</v>
-      </c>
-      <c r="D37" t="n">
-        <v>172.6845</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>52.4082</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-28.8389</v>
-      </c>
-      <c r="D38" t="n">
-        <v>133.6552</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.205</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>89.8909</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-41.4747</v>
-      </c>
-      <c r="D39" t="n">
-        <v>221.2566</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.179</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>-102.5887</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-421.4204</v>
-      </c>
-      <c r="D40" t="n">
-        <v>216.2431</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.527</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>-4.7684</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-9.1067</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-0.4301</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>-0.4392</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.5649</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.6866</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.444</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0344</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1.7667e-02</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>955.3328</v>
-      </c>
-      <c r="C50" t="n">
-        <v>616.9353</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1293.7302</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>92.8733</v>
-      </c>
-      <c r="C51" t="n">
-        <v>3.7343</v>
-      </c>
-      <c r="D51" t="n">
-        <v>182.0123</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.041</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>-106.1958</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-402.125</v>
-      </c>
-      <c r="D52" t="n">
-        <v>189.7334</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.481</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>-6.3503</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-11.1599</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-1.5407</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.010</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>-0.1928</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.4473</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.0617</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.763</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/XRCC3_LUSC_Tables.xlsx
+++ b/result/XRCC3_LUSC_Tables.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2062,6 +2063,966 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0314</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.1656e-02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>841.7472</v>
+      </c>
+      <c r="C8" t="n">
+        <v>528.6834</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1154.8109</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>89.13720000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9.273300000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>169.0011</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-5.1626</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-9.4291</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.8961</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.4115</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.5348</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7118</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.472</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>25.2729</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-18.7692</v>
+      </c>
+      <c r="D12" t="n">
+        <v>69.315</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.260</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.0367</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3.4940e-02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>807.9279</v>
+      </c>
+      <c r="C20" t="n">
+        <v>489.0994</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1126.7564</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>91.758</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10.7892</v>
+      </c>
+      <c r="D21" t="n">
+        <v>172.7267</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-88.9134</v>
+      </c>
+      <c r="D22" t="n">
+        <v>89.2538</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.997</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>32.8988</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-105.9739</v>
+      </c>
+      <c r="D23" t="n">
+        <v>171.7714</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.642</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-119.1153</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-332.4124</v>
+      </c>
+      <c r="D24" t="n">
+        <v>94.1818</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-4.8781</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-9.1716</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.5846</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.3601</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.4868</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.7665999999999999</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0.530</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>31.5869</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-22.4827</v>
+      </c>
+      <c r="D27" t="n">
+        <v>85.65649999999999</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.251</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0.0375</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3.3139e-02</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>852.0059</v>
+      </c>
+      <c r="C35" t="n">
+        <v>532.668</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1171.3438</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>93.71169999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>13.1097</v>
+      </c>
+      <c r="D36" t="n">
+        <v>174.3137</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>60.8624</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-46.0591</v>
+      </c>
+      <c r="D37" t="n">
+        <v>167.7839</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>110.6762</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-68.8283</v>
+      </c>
+      <c r="D38" t="n">
+        <v>290.1807</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.226</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-88.4816</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-429.8603</v>
+      </c>
+      <c r="D39" t="n">
+        <v>252.8971</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.611</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-4.8408</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-9.214700000000001</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.4669</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0.030</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.4547</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.5877</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6782</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0.431</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-7.952</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-76.8449</v>
+      </c>
+      <c r="D42" t="n">
+        <v>60.9409</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0.821</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0.0367</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2.6244e-02</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>914.2578999999999</v>
+      </c>
+      <c r="C50" t="n">
+        <v>554.0359999999999</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1274.4798</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>91.62350000000001</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.0922</v>
+      </c>
+      <c r="D51" t="n">
+        <v>181.1548</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.045</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-155.6327</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-476.7119</v>
+      </c>
+      <c r="D52" t="n">
+        <v>165.4466</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.341</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-6.2398</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-11.1059</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-1.3736</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>-0.2116</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-1.4718</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.0487</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0.741</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>21.2135</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-30.6793</v>
+      </c>
+      <c r="D55" t="n">
+        <v>73.1062</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.422</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/XRCC3_LUSC_Tables.xlsx
+++ b/result/XRCC3_LUSC_Tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1745,7 +1746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1792,7 +1793,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.027</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1804,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>0.996</v>
@@ -1813,242 +1814,112 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>0.940</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>XRCC3group_Low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>1.287</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.954</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.738</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>0.099</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDKN2AExpression</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.881</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.774</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.970</t>
+          <t>0.212</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOX2Expression</t>
+          <t>pathologic_stage_2.0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>1.037</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.732</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.469</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.839</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PIK3CAExpression</t>
+          <t>pathologic_stage_3.0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>1.411</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.947</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2.102</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>0.091</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NOTCH1Expression</t>
+          <t>pathologic_stage_4.0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2.942</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>1.172</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>7.383</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.745</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>XRCC3group_High</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>505182.941</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.993</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>XRCC3group_Low</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>649083.7560000001</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.993</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>gender_MALE</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.259</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.879</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.804</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.208</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage_2.0</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.088</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.551</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.639</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pathologic_stage_3.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.457</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.181</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.992</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.187</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7.541</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.020</t>
+          <t>0.022</t>
         </is>
       </c>
     </row>
@@ -2063,18 +1934,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Clinical Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Hazard Ratio (HR)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2094,923 +1965,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>== [ Model: Base Model (No Stage) ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.996</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0314</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>XRCC3group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.1656e-02</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>841.7472</v>
-      </c>
-      <c r="C8" t="n">
-        <v>528.6834</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1154.8109</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>89.13720000000001</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.273300000000001</v>
-      </c>
-      <c r="D9" t="n">
-        <v>169.0011</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.029</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-5.1626</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-9.4291</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.8961</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.018</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-0.4115</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.5348</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.7118</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.472</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>25.2729</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-18.7692</v>
-      </c>
-      <c r="D12" t="n">
-        <v>69.315</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.260</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <f>== [ Model: Base + Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0.0367</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3.4940e-02</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>807.9279</v>
-      </c>
-      <c r="C20" t="n">
-        <v>489.0994</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1126.7564</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>91.758</v>
-      </c>
-      <c r="C21" t="n">
-        <v>10.7892</v>
-      </c>
-      <c r="D21" t="n">
-        <v>172.7267</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0.026</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.1702</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-88.9134</v>
-      </c>
-      <c r="D22" t="n">
-        <v>89.2538</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.997</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>32.8988</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-105.9739</v>
-      </c>
-      <c r="D23" t="n">
-        <v>171.7714</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.642</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>-119.1153</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-332.4124</v>
-      </c>
-      <c r="D24" t="n">
-        <v>94.1818</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-4.8781</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-9.1716</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-0.5846</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.026</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>-0.3601</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-1.4868</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.7665999999999999</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.530</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>31.5869</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-22.4827</v>
-      </c>
-      <c r="D27" t="n">
-        <v>85.65649999999999</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.251</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <f>== [ Model: Base + Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>0.0375</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3.3139e-02</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>852.0059</v>
-      </c>
-      <c r="C35" t="n">
-        <v>532.668</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1171.3438</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>93.71169999999999</v>
-      </c>
-      <c r="C36" t="n">
-        <v>13.1097</v>
-      </c>
-      <c r="D36" t="n">
-        <v>174.3137</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>60.8624</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-46.0591</v>
-      </c>
-      <c r="D37" t="n">
-        <v>167.7839</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.264</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>110.6762</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-68.8283</v>
-      </c>
-      <c r="D38" t="n">
-        <v>290.1807</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.226</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>-88.4816</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-429.8603</v>
-      </c>
-      <c r="D39" t="n">
-        <v>252.8971</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.611</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>-4.8408</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-9.214700000000001</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.4669</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.030</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>-0.4547</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-1.5877</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.6782</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.431</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>-7.952</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-76.8449</v>
-      </c>
-      <c r="D42" t="n">
-        <v>60.9409</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.821</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>== [ Model: Base + Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0367</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2.6244e-02</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>914.2578999999999</v>
-      </c>
-      <c r="C50" t="n">
-        <v>554.0359999999999</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1274.4798</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>91.62350000000001</v>
-      </c>
-      <c r="C51" t="n">
-        <v>2.0922</v>
-      </c>
-      <c r="D51" t="n">
-        <v>181.1548</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.045</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>-155.6327</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-476.7119</v>
-      </c>
-      <c r="D52" t="n">
-        <v>165.4466</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.341</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>-6.2398</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-11.1059</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-1.3736</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.012</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>-0.2116</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.4718</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.0487</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.741</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>21.2135</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-30.6793</v>
-      </c>
-      <c r="D55" t="n">
-        <v>73.1062</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0.422</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3023,6 +2080,1117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0278</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>9.2105e-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>891.1136</v>
+      </c>
+      <c r="C8" t="n">
+        <v>596.1462</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1186.081</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>91.24550000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11.8179</v>
+      </c>
+      <c r="D9" t="n">
+        <v>170.6732</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-5.2818</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-9.503</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.0606</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.014</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.4145</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.5327</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.467</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0349</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.5843e-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>847.3088</v>
+      </c>
+      <c r="C19" t="n">
+        <v>543.1007</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1151.5169</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>92.3857</v>
+      </c>
+      <c r="C20" t="n">
+        <v>12.2633</v>
+      </c>
+      <c r="D20" t="n">
+        <v>172.508</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>37.7938</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-41.6969</v>
+      </c>
+      <c r="D21" t="n">
+        <v>117.2846</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.351</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>70.2186</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-29.0241</v>
+      </c>
+      <c r="D22" t="n">
+        <v>169.4614</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.165</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-84.5162</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-378.0097</v>
+      </c>
+      <c r="D23" t="n">
+        <v>208.9772</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.572</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-4.9509</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-9.2342</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.6676</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.4451</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.5705</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.6802</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.437</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0334</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3.1411e-02</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>857.9524</v>
+      </c>
+      <c r="C33" t="n">
+        <v>556.5856</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1159.3192</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>93.1567</v>
+      </c>
+      <c r="C34" t="n">
+        <v>12.5844</v>
+      </c>
+      <c r="D34" t="n">
+        <v>173.7291</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>10.7209</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-75.8443</v>
+      </c>
+      <c r="D35" t="n">
+        <v>97.2861</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.808</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>74.2885</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-47.1227</v>
+      </c>
+      <c r="D36" t="n">
+        <v>195.6997</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.230</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-59.6083</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-246.2184</v>
+      </c>
+      <c r="D37" t="n">
+        <v>127.0018</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.530</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-5.0534</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-9.2911</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.8157</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.020</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.3616</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.483</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.7599</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.527</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0363</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2.1411e-02</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>837.4939000000001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>530.8721</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1144.1157</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>92.765</v>
+      </c>
+      <c r="C48" t="n">
+        <v>12.8455</v>
+      </c>
+      <c r="D48" t="n">
+        <v>172.6845</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>52.4082</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-28.8389</v>
+      </c>
+      <c r="D49" t="n">
+        <v>133.6552</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.205</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>89.8909</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-41.4747</v>
+      </c>
+      <c r="D50" t="n">
+        <v>221.2566</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.179</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-102.5887</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-421.4204</v>
+      </c>
+      <c r="D51" t="n">
+        <v>216.2431</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.527</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-4.7684</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-9.1067</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.4301</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.4392</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-1.5649</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.6866</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0344</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1.7667e-02</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>955.3328</v>
+      </c>
+      <c r="C61" t="n">
+        <v>616.9353</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1293.7302</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>92.8733</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3.7343</v>
+      </c>
+      <c r="D62" t="n">
+        <v>182.0123</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.041</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-106.1958</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-402.125</v>
+      </c>
+      <c r="D63" t="n">
+        <v>189.7334</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.481</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>-6.3503</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-11.1599</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-1.5407</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.1928</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.4473</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.0617</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0.763</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/XRCC3_LUSC_Tables.xlsx
+++ b/result/XRCC3_LUSC_Tables.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,18 +439,17 @@
           <t>Clinical Characteristics</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -465,7 +464,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -474,17 +472,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="C3" t="n">
-        <v>109</v>
-      </c>
-      <c r="D3" t="n">
         <v>79</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.008</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.005</t>
         </is>
       </c>
     </row>
@@ -495,15 +490,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="C4" t="n">
-        <v>134</v>
-      </c>
-      <c r="D4" t="n">
         <v>165</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -514,7 +506,6 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -523,17 +514,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
-      </c>
-      <c r="D6" t="n">
         <v>73</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.104</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.041</t>
         </is>
       </c>
     </row>
@@ -544,15 +532,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>190</v>
-      </c>
-      <c r="D7" t="n">
         <v>171</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -563,7 +548,6 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -572,17 +556,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="C9" t="n">
-        <v>103</v>
-      </c>
-      <c r="D9" t="n">
         <v>134</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.061</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -593,15 +574,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C10" t="n">
-        <v>82</v>
-      </c>
-      <c r="D10" t="n">
         <v>74</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -610,15 +588,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
-      </c>
-      <c r="D11" t="n">
         <v>30</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -627,15 +602,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -646,7 +618,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -655,17 +626,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="C14" t="n">
-        <v>201</v>
-      </c>
-      <c r="D14" t="n">
         <v>199</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.919</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.698</t>
         </is>
       </c>
     </row>
@@ -676,15 +644,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -695,7 +660,6 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -704,17 +668,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="C17" t="n">
-        <v>142</v>
-      </c>
-      <c r="D17" t="n">
         <v>168</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.231</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.057</t>
         </is>
       </c>
     </row>
@@ -725,15 +686,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C18" t="n">
-        <v>70</v>
-      </c>
-      <c r="D18" t="n">
         <v>56</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -742,15 +700,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
-      </c>
-      <c r="D19" t="n">
         <v>14</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -759,15 +714,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -778,7 +730,6 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -787,17 +738,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
-      </c>
-      <c r="D22" t="n">
         <v>66</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.077</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.047</t>
         </is>
       </c>
     </row>
@@ -808,15 +756,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="C23" t="n">
-        <v>149</v>
-      </c>
-      <c r="D23" t="n">
         <v>137</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -825,15 +770,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C24" t="n">
-        <v>41</v>
-      </c>
-      <c r="D24" t="n">
         <v>29</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -842,15 +784,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
-      </c>
-      <c r="D25" t="n">
         <v>12</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -861,7 +800,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -870,17 +808,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C27" t="n">
-        <v>39</v>
-      </c>
-      <c r="D27" t="n">
         <v>37</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.884</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.803</t>
         </is>
       </c>
     </row>
@@ -891,15 +826,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>205</v>
       </c>
       <c r="C28" t="n">
-        <v>205</v>
-      </c>
-      <c r="D28" t="n">
         <v>207</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2080,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,15 +2028,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -2118,7 +2045,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2133,7 +2059,6 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2148,7 +2073,6 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2163,7 +2087,6 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2178,7 +2101,6 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2189,7 +2111,6 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2200,13 +2121,12 @@
       <c r="B8" t="n">
         <v>891.1136</v>
       </c>
-      <c r="C8" t="n">
-        <v>596.1462</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1186.081</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>596.146-1186.081</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2221,13 +2141,12 @@
       <c r="B9" t="n">
         <v>91.24550000000001</v>
       </c>
-      <c r="C9" t="n">
-        <v>11.8179</v>
-      </c>
-      <c r="D9" t="n">
-        <v>170.6732</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11.818-170.673</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>0.024</t>
         </is>
@@ -2242,13 +2161,12 @@
       <c r="B10" t="n">
         <v>-5.2818</v>
       </c>
-      <c r="C10" t="n">
-        <v>-9.503</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-1.0606</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-9.503--1.061</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.014</t>
         </is>
@@ -2263,13 +2181,12 @@
       <c r="B11" t="n">
         <v>-0.4145</v>
       </c>
-      <c r="C11" t="n">
-        <v>-1.5327</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.7036</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-1.533-0.704</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.467</t>
         </is>
@@ -2280,7 +2197,6 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13">
@@ -2290,7 +2206,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2305,7 +2220,6 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2320,7 +2234,6 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2335,7 +2248,6 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2350,7 +2262,6 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2361,7 +2272,6 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2372,13 +2282,12 @@
       <c r="B19" t="n">
         <v>847.3088</v>
       </c>
-      <c r="C19" t="n">
-        <v>543.1007</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1151.5169</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>543.1007-1151.5169</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2393,13 +2302,12 @@
       <c r="B20" t="n">
         <v>92.3857</v>
       </c>
-      <c r="C20" t="n">
-        <v>12.2633</v>
-      </c>
-      <c r="D20" t="n">
-        <v>172.508</v>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>12.2633-172.508</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>0.024</t>
         </is>
@@ -2414,13 +2322,12 @@
       <c r="B21" t="n">
         <v>37.7938</v>
       </c>
-      <c r="C21" t="n">
-        <v>-41.6969</v>
-      </c>
-      <c r="D21" t="n">
-        <v>117.2846</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-41.6969-117.2846</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>0.351</t>
         </is>
@@ -2435,13 +2342,12 @@
       <c r="B22" t="n">
         <v>70.2186</v>
       </c>
-      <c r="C22" t="n">
-        <v>-29.0241</v>
-      </c>
-      <c r="D22" t="n">
-        <v>169.4614</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-29.0241-169.4614</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>0.165</t>
         </is>
@@ -2456,13 +2362,12 @@
       <c r="B23" t="n">
         <v>-84.5162</v>
       </c>
-      <c r="C23" t="n">
-        <v>-378.0097</v>
-      </c>
-      <c r="D23" t="n">
-        <v>208.9772</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-378.0097-208.9772</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>0.572</t>
         </is>
@@ -2477,13 +2382,12 @@
       <c r="B24" t="n">
         <v>-4.9509</v>
       </c>
-      <c r="C24" t="n">
-        <v>-9.2342</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-0.6676</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-9.2342--0.6676</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>0.024</t>
         </is>
@@ -2498,13 +2402,12 @@
       <c r="B25" t="n">
         <v>-0.4451</v>
       </c>
-      <c r="C25" t="n">
-        <v>-1.5705</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.6802</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-1.5705-0.6802</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.437</t>
         </is>
@@ -2515,7 +2418,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27">
@@ -2525,7 +2427,6 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2540,7 +2441,6 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2555,7 +2455,6 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2570,7 +2469,6 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2585,7 +2483,6 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2596,7 +2493,6 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2607,13 +2503,12 @@
       <c r="B33" t="n">
         <v>857.9524</v>
       </c>
-      <c r="C33" t="n">
-        <v>556.5856</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1159.3192</v>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>556.5856-1159.3192</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2628,13 +2523,12 @@
       <c r="B34" t="n">
         <v>93.1567</v>
       </c>
-      <c r="C34" t="n">
-        <v>12.5844</v>
-      </c>
-      <c r="D34" t="n">
-        <v>173.7291</v>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>12.5844-173.7291</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>0.024</t>
         </is>
@@ -2649,13 +2543,12 @@
       <c r="B35" t="n">
         <v>10.7209</v>
       </c>
-      <c r="C35" t="n">
-        <v>-75.8443</v>
-      </c>
-      <c r="D35" t="n">
-        <v>97.2861</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-75.8443-97.2861</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>0.808</t>
         </is>
@@ -2670,13 +2563,12 @@
       <c r="B36" t="n">
         <v>74.2885</v>
       </c>
-      <c r="C36" t="n">
-        <v>-47.1227</v>
-      </c>
-      <c r="D36" t="n">
-        <v>195.6997</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-47.1227-195.6997</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>0.230</t>
         </is>
@@ -2691,13 +2583,12 @@
       <c r="B37" t="n">
         <v>-59.6083</v>
       </c>
-      <c r="C37" t="n">
-        <v>-246.2184</v>
-      </c>
-      <c r="D37" t="n">
-        <v>127.0018</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-246.2184-127.0018</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>0.530</t>
         </is>
@@ -2712,13 +2603,12 @@
       <c r="B38" t="n">
         <v>-5.0534</v>
       </c>
-      <c r="C38" t="n">
-        <v>-9.2911</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-0.8157</v>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-9.2911--0.8157</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>0.020</t>
         </is>
@@ -2733,13 +2623,12 @@
       <c r="B39" t="n">
         <v>-0.3616</v>
       </c>
-      <c r="C39" t="n">
-        <v>-1.483</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.7599</v>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-1.483-0.7599</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>0.527</t>
         </is>
@@ -2750,7 +2639,6 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41">
@@ -2760,7 +2648,6 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2775,7 +2662,6 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2790,7 +2676,6 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2805,7 +2690,6 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2820,7 +2704,6 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2831,7 +2714,6 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2842,13 +2724,12 @@
       <c r="B47" t="n">
         <v>837.4939000000001</v>
       </c>
-      <c r="C47" t="n">
-        <v>530.8721</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1144.1157</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>530.8721-1144.1157</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2863,13 +2744,12 @@
       <c r="B48" t="n">
         <v>92.765</v>
       </c>
-      <c r="C48" t="n">
-        <v>12.8455</v>
-      </c>
-      <c r="D48" t="n">
-        <v>172.6845</v>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>12.8455-172.6845</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>0.023</t>
         </is>
@@ -2884,13 +2764,12 @@
       <c r="B49" t="n">
         <v>52.4082</v>
       </c>
-      <c r="C49" t="n">
-        <v>-28.8389</v>
-      </c>
-      <c r="D49" t="n">
-        <v>133.6552</v>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-28.8389-133.6552</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>0.205</t>
         </is>
@@ -2905,13 +2784,12 @@
       <c r="B50" t="n">
         <v>89.8909</v>
       </c>
-      <c r="C50" t="n">
-        <v>-41.4747</v>
-      </c>
-      <c r="D50" t="n">
-        <v>221.2566</v>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-41.4747-221.2566</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>0.179</t>
         </is>
@@ -2926,13 +2804,12 @@
       <c r="B51" t="n">
         <v>-102.5887</v>
       </c>
-      <c r="C51" t="n">
-        <v>-421.4204</v>
-      </c>
-      <c r="D51" t="n">
-        <v>216.2431</v>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-421.4204-216.2431</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>0.527</t>
         </is>
@@ -2947,13 +2824,12 @@
       <c r="B52" t="n">
         <v>-4.7684</v>
       </c>
-      <c r="C52" t="n">
-        <v>-9.1067</v>
-      </c>
-      <c r="D52" t="n">
-        <v>-0.4301</v>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-9.1067--0.4301</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>0.031</t>
         </is>
@@ -2968,13 +2844,12 @@
       <c r="B53" t="n">
         <v>-0.4392</v>
       </c>
-      <c r="C53" t="n">
-        <v>-1.5649</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.6866</v>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-1.5649-0.6866</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>0.444</t>
         </is>
@@ -2985,7 +2860,6 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55">
@@ -2995,7 +2869,6 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3010,7 +2883,6 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3025,7 +2897,6 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3040,7 +2911,6 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3055,7 +2925,6 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3066,7 +2935,6 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3077,13 +2945,12 @@
       <c r="B61" t="n">
         <v>955.3328</v>
       </c>
-      <c r="C61" t="n">
-        <v>616.9353</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1293.7302</v>
-      </c>
-      <c r="E61" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>616.9353-1293.7302</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -3098,13 +2965,12 @@
       <c r="B62" t="n">
         <v>92.8733</v>
       </c>
-      <c r="C62" t="n">
-        <v>3.7343</v>
-      </c>
-      <c r="D62" t="n">
-        <v>182.0123</v>
-      </c>
-      <c r="E62" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3.7343-182.0123</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>0.041</t>
         </is>
@@ -3119,13 +2985,12 @@
       <c r="B63" t="n">
         <v>-106.1958</v>
       </c>
-      <c r="C63" t="n">
-        <v>-402.125</v>
-      </c>
-      <c r="D63" t="n">
-        <v>189.7334</v>
-      </c>
-      <c r="E63" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-402.125-189.7334</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>0.481</t>
         </is>
@@ -3140,13 +3005,12 @@
       <c r="B64" t="n">
         <v>-6.3503</v>
       </c>
-      <c r="C64" t="n">
-        <v>-11.1599</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-1.5407</v>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-11.1599--1.5407</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
@@ -3161,13 +3025,12 @@
       <c r="B65" t="n">
         <v>-0.1928</v>
       </c>
-      <c r="C65" t="n">
-        <v>-1.4473</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1.0617</v>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-1.4473-1.0617</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>0.763</t>
         </is>
@@ -3178,7 +3041,6 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/result/XRCC3_LUSC_Tables.xlsx
+++ b/result/XRCC3_LUSC_Tables.xlsx
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>891.1136</v>
+        <v>891.114</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91.24550000000001</v>
+        <v>91.246</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-5.2818</v>
+        <v>-5.282</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.4145</v>
+        <v>-0.415</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2280,11 +2280,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>847.3088</v>
+        <v>847.309</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>543.1007-1151.5169</t>
+          <t>543.101-1151.517</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>92.3857</v>
+        <v>92.386</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12.2633-172.508</t>
+          <t>12.263-172.508</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2320,11 +2320,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>37.7938</v>
+        <v>37.794</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-41.6969-117.2846</t>
+          <t>-41.697-117.285</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2340,11 +2340,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>70.2186</v>
+        <v>70.21899999999999</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-29.0241-169.4614</t>
+          <t>-29.024-169.461</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2360,11 +2360,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-84.5162</v>
+        <v>-84.51600000000001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-378.0097-208.9772</t>
+          <t>-378.01-208.977</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2380,11 +2380,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-4.9509</v>
+        <v>-4.951</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-9.2342--0.6676</t>
+          <t>-9.234--0.668</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2400,11 +2400,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4451</v>
+        <v>-0.445</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.5705-0.6802</t>
+          <t>-1.571-0.68</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2501,11 +2501,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>857.9524</v>
+        <v>857.952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>556.5856-1159.3192</t>
+          <t>556.586-1159.319</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2521,11 +2521,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>93.1567</v>
+        <v>93.157</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12.5844-173.7291</t>
+          <t>12.584-173.729</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2541,11 +2541,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10.7209</v>
+        <v>10.721</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-75.8443-97.2861</t>
+          <t>-75.844-97.286</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2561,11 +2561,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>74.2885</v>
+        <v>74.288</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-47.1227-195.6997</t>
+          <t>-47.123-195.7</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2581,11 +2581,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-59.6083</v>
+        <v>-59.608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-246.2184-127.0018</t>
+          <t>-246.218-127.002</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2601,11 +2601,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-5.0534</v>
+        <v>-5.053</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-9.2911--0.8157</t>
+          <t>-9.291--0.816</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2621,11 +2621,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.3616</v>
+        <v>-0.362</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-1.483-0.7599</t>
+          <t>-1.483-0.76</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>837.4939000000001</v>
+        <v>837.494</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>530.8721-1144.1157</t>
+          <t>530.872-1144.116</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12.8455-172.6845</t>
+          <t>12.846-172.684</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52.4082</v>
+        <v>52.408</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-28.8389-133.6552</t>
+          <t>-28.839-133.655</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2782,11 +2782,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>89.8909</v>
+        <v>89.89100000000001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-41.4747-221.2566</t>
+          <t>-41.475-221.257</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2802,11 +2802,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-102.5887</v>
+        <v>-102.589</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-421.4204-216.2431</t>
+          <t>-421.42-216.243</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2822,11 +2822,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-4.7684</v>
+        <v>-4.768</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-9.1067--0.4301</t>
+          <t>-9.107--0.43</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2842,11 +2842,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.4392</v>
+        <v>-0.439</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-1.5649-0.6866</t>
+          <t>-1.565-0.687</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2943,11 +2943,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>955.3328</v>
+        <v>955.333</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>616.9353-1293.7302</t>
+          <t>616.935-1293.73</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2963,11 +2963,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>92.8733</v>
+        <v>92.873</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3.7343-182.0123</t>
+          <t>3.734-182.012</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2983,11 +2983,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-106.1958</v>
+        <v>-106.196</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-402.125-189.7334</t>
+          <t>-402.125-189.733</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3003,11 +3003,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-6.3503</v>
+        <v>-6.35</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>-11.1599--1.5407</t>
+          <t>-11.16--1.541</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3023,11 +3023,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.1928</v>
+        <v>-0.193</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-1.4473-1.0617</t>
+          <t>-1.447-1.062</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
